--- a/data/SmartVMS_Mau_KichBan_KiemThu.xlsx
+++ b/data/SmartVMS_Mau_KichBan_KiemThu.xlsx
@@ -1,58 +1,434 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Mau_KichBan" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Mau_KichBan_Chuan" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="📖 Hướng Dẫn Sử Dụng" state="visible" r:id="rId5"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="73">
+  <si>
+    <t>🎯 SMARTVMS LOCAL SINGLESITE 2026 — DANH MỤC KỊCH BẢN KIỂM THỬ CHUẨN HÓA (ISO 29119-3)</t>
+  </si>
+  <si>
+    <t>📋 Tiêu chuẩn: ISO/IEC/IEEE 29119-3:2021 &amp; ISO/IEC 25010 | Quy mô: 12 Phân hệ | Đợt 1 Regression: 155 Đạt / 2 Lỗi (98.7% Pass Rate) | QA Lead: Nguyễn Văn Huy</t>
+  </si>
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Mã Test Case (*)</t>
+  </si>
+  <si>
+    <t>Phân hệ (Module) (*)</t>
+  </si>
+  <si>
+    <t>Tiêu đề kịch bản (*)</t>
+  </si>
+  <si>
+    <t>Mức ưu tiên</t>
+  </si>
+  <si>
+    <t>Loại kiểm thử</t>
+  </si>
+  <si>
+    <t>Bộ kịch bản</t>
+  </si>
+  <si>
+    <t>Nền tảng</t>
+  </si>
+  <si>
+    <t>Điều kiện tiên quyết (Preconditions)</t>
+  </si>
+  <si>
+    <t>Dữ liệu kiểm thử (Test Data)</t>
+  </si>
+  <si>
+    <t>Quy trình các bước (Test Steps)</t>
+  </si>
+  <si>
+    <t>Kết quả kỳ vọng (Expected Results)</t>
+  </si>
+  <si>
+    <t>Trạng thái Test</t>
+  </si>
+  <si>
+    <t>Ghi chú kỹ thuật</t>
+  </si>
+  <si>
+    <t>TC-AUTH-001</t>
+  </si>
+  <si>
+    <t>M01 - Xác thực &amp; Quản lý Ca trực</t>
+  </si>
+  <si>
+    <t>Đăng nhập Trạm gác hợp lệ bằng tài khoản trạm (Không mật khẩu)</t>
+  </si>
+  <si>
+    <t>🔴 P1 - Critical</t>
+  </si>
+  <si>
+    <t>Chức năng</t>
+  </si>
+  <si>
+    <t>REGRESSION</t>
+  </si>
+  <si>
+    <t>Giao diện Web Trực ban</t>
+  </si>
+  <si>
+    <t>Backend API đang chạy; Cán bộ "NV001" (Nguyễn Văn Huy) có trạng thái kích hoạt trong CSDL.</t>
+  </si>
+  <si>
+    <t>Tên đăng nhập: "Nv001a1" (không cần mật khẩu).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Truy cập trang web Trạm gác (/staff.html).
+2. Nhập Tên đăng nhập trạm (vd: Nv001a1), nhấn Đăng nhập (hệ thống trạm không yêu cầu mật khẩu).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Hệ thống tự động chuẩn hóa chữ thường, xác thực thành công và lưu Token đăng nhập trạm.
+• Nếu trạm chưa có ca trực nào đang mở, popup "Xác nhận chụp ảnh vào ca" sẽ tự động hiện lên.</t>
+  </si>
+  <si>
+    <t>✅ ĐẠT (Pass)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>TC-AUTH-002</t>
+  </si>
+  <si>
+    <t>Đăng nhập trạm không phân biệt hoa/thường</t>
+  </si>
+  <si>
+    <t>🟢 P4 - Low</t>
+  </si>
+  <si>
+    <t>Trang đăng nhập trạm (/staff.html) đang mở.</t>
+  </si>
+  <si>
+    <t>Nhập xen kẽ hoa thường: "NV001A1", "nv001a1", hoặc "Nv001a1".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập username xen kẽ chữ hoa chữ thường.
+2. Nhấn nút Đăng nhập.</t>
+  </si>
+  <si>
+    <t>• Hệ thống tự động chuẩn hóa chữ thường và đăng nhập thành công, không phát sinh lỗi.</t>
+  </si>
+  <si>
+    <t>TC-AUTH-003</t>
+  </si>
+  <si>
+    <t>Đăng nhập trạm thất bại: Tên tài khoản không tồn tại</t>
+  </si>
+  <si>
+    <t>Tên đăng nhập không tồn tại: "khongtontai999".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập tài khoản không tồn tại trong hệ thống.
+2. Nhấn Đăng nhập.</t>
+  </si>
+  <si>
+    <t>• Hệ thống chặn lại và hiển thị thông báo: "User không hợp lệ hoặc nhân viên chưa được kích hoạt."</t>
+  </si>
+  <si>
+    <t>TC-AUTH-004</t>
+  </si>
+  <si>
+    <t>Đăng nhập trạm thất bại: Tài khoản bị khóa (Inactive)</t>
+  </si>
+  <si>
+    <t>Tài khoản nhân viên đã bị tắt cờ IsActive (Inactive) trong Admin Staff Management.</t>
+  </si>
+  <si>
+    <t>Tên đăng nhập của nhân viên bị khóa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Nhập tài khoản nhân viên đã bị vô hiệu hóa.
+2. Nhấn Đăng nhập.</t>
+  </si>
+  <si>
+    <t>• Hệ thống từ chối đăng nhập, hiển thị thông báo: "User không hợp lệ hoặc nhân viên chưa được kích hoạt."</t>
+  </si>
+  <si>
+    <t>TC-AUTH-005</t>
+  </si>
+  <si>
+    <t>Xử lý xung đột phiên trạm: Phát hiện trạm đang có phiên mở dở dang và Ép Đăng Xuất Phiên Cũ</t>
+  </si>
+  <si>
+    <t>🟠 P2 - Important</t>
+  </si>
+  <si>
+    <t>Trạm gác "STATION_A" đang có 1 ca trực dở dang chưa được đóng bởi phiên trước.</t>
+  </si>
+  <si>
+    <t>Tài khoản cán bộ nhận ca: "Nv001a1".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Tại trang /staff.html, đăng nhập vào tài khoản trạm đang có phiên trực mở dở dang hoặc đang đăng nhập ở một thiết bị khác.
+2. Quan sát hộp cảnh báo màu hồng viền đỏ "CẢNH BÁO: TÀI KHOẢN ĐANG HOẠT ĐỘNG" cùng nút hành động màu đỏ "Ép Đăng Xuất Phiên Cũ".
+3. Nhấn nút "Ép Đăng Xuất Phiên Cũ".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Hệ thống gửi request đăng nhập kèm forceLogout = true tới API /station/auth/login.
+• Phiên làm việc ở thiết bị trước bị ngắt kết nối ngay lập tức, quyền kiểm soát ca trực được chuyển sang thiết bị này.
+• Hệ thống mở giao diện Mở ca trực (StartShiftModal) để cán bộ chụp ảnh hoặc quẹt CCCD vào ca chính quy.</t>
+  </si>
+  <si>
+    <t>📖 HƯỚNG DẪN QUẢN LÝ &amp; NHẬP LIỆU KỊCH BẢN KIỂM THỬ SMARTVMS</t>
+  </si>
+  <si>
+    <t>MỤC</t>
+  </si>
+  <si>
+    <t>NỘI DUNG HƯỚNG DẪN CHI TIẾT</t>
+  </si>
+  <si>
+    <t>LƯU Ý QUAN TRỌNG</t>
+  </si>
+  <si>
+    <t>1. Cấu trúc kịch bản</t>
+  </si>
+  <si>
+    <t>File Excel được chuẩn hóa theo chuẩn quốc tế ISO/IEC/IEEE 29119-3:2021 và ISO/IEC 25010.</t>
+  </si>
+  <si>
+    <t>Mã Test Case và Tiêu đề là bắt buộc, không được để trống.</t>
+  </si>
+  <si>
+    <t>2. Chỉnh sửa kịch bản</t>
+  </si>
+  <si>
+    <t>Bạn có thể trực tiếp sửa các bước thực hiện, kết quả kỳ vọng, mức ưu tiên ngay trong file này.</t>
+  </si>
+  <si>
+    <t>Khi viết nhiều bước, nhấn Alt + Enter trong ô để xuống dòng (1. ... 2. ...).</t>
+  </si>
+  <si>
+    <t>3. Thêm kịch bản mới</t>
+  </si>
+  <si>
+    <t>Thêm dòng mới vào cuối bảng với mã kịch bản theo định dạng: TC-[MÃ PHÂN HỆ]-[SỐ TT].</t>
+  </si>
+  <si>
+    <t>Ví dụ: TC-AUTH-015, TC-CKIN-020.</t>
+  </si>
+  <si>
+    <t>4. Nạp vào Web Test Hub</t>
+  </si>
+  <si>
+    <t>Mở trang web Quản lý kịch bản (admin/testcases.html) -&gt; Bấm nút [📗 Nhập Excel (.xlsx)] -&gt; Chọn file này.</t>
+  </si>
+  <si>
+    <t>Hệ thống sẽ tự động cập nhật toàn bộ kịch bản, đợt test và ma trận phân công.</t>
+  </si>
+  <si>
+    <t>5. Đồng bộ nhiều máy</t>
+  </si>
+  <si>
+    <t>Sau khi nạp xong, danh mục sẽ tự động được lưu vào máy chủ LAN và Supabase Cloud.</t>
+  </si>
+  <si>
+    <t>Các tester khác chỉ cần mở trình duyệt là thấy ngay danh mục mới.</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
-    <font>
-      <sz val="12"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="19" x14ac:knownFonts="1">
+    <font>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <color rgb="FFE2E8F0"/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10.5"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF64748B"/>
+      <sz val="9.5"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1E3A8A"/>
+      <sz val="10"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0F172A"/>
+      <sz val="9.5"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0F172A"/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFDC2626"/>
+      <sz val="9"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <color rgb="FF334155"/>
+      <sz val="9"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <color rgb="FF334155"/>
+      <sz val="9"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <color rgb="FF0F172A"/>
+      <sz val="9.5"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <color rgb="FF15803D"/>
+      <sz val="9.5"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF16A34A"/>
+      <sz val="9.5"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF64748B"/>
+      <sz val="9"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF475569"/>
+      <sz val="9"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFEA580C"/>
+      <sz val="9"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E3A8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEDD5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF312E81"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4338CA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F3FF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -60,18 +436,158 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3B82F6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3B82F6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1E3A8A"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1E3A8A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="35">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,202 +912,433 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF2563EB"/>
+  </sheetPr>
+  <dimension ref="A1:N9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="45.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="40.83203125" customWidth="1"/>
-    <col min="10" max="10" width="30.83203125" customWidth="1"/>
-    <col min="11" max="11" width="45.83203125" customWidth="1"/>
-    <col min="12" max="12" width="45.83203125" customWidth="1"/>
-    <col min="13" max="13" width="30.83203125" customWidth="1"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="38" customWidth="1"/>
+    <col min="10" max="10" width="34" customWidth="1"/>
+    <col min="11" max="12" width="62" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Mã Test Case (*)</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Phân hệ (*)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Tiêu đề kịch bản (*)</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Mức ưu tiên</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Loại kiểm thử</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Bộ kịch bản</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Nền tảng</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Mã SRS</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Điều kiện tiên quyết</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Dữ liệu kiểm thử</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Các bước thực hiện</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Kết quả kỳ vọng</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Ghi chú</v>
-      </c>
-    </row>
-    <row r="2" xml:space="preserve">
-      <c r="A2" t="str">
-        <v>TC-AUTH-001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>M01</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Đăng nhập Trạm gác hợp lệ bằng tài khoản trạm (Không mật khẩu)</v>
-      </c>
-      <c r="D2" t="str">
-        <v>P1</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Chức năng</v>
-      </c>
-      <c r="F2" t="str">
-        <v>SMOKE</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Web Trực ban</v>
-      </c>
-      <c r="H2" t="str">
-        <v>SRS-AUTH-01</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Hệ thống SmartVMS Local SingleSite đang hoạt động. Trạm gác B01 đã được tạo và kích hoạt.</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Station Code = B01</v>
-      </c>
-      <c r="K2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Mở trình duyệt Web tại http://smartvms.local/station
-2. Nhập mã trạm: b01
-3. Bấm Đăng nhập vào bốt trực</v>
-      </c>
-      <c r="L2" t="str" xml:space="preserve">
-        <v xml:space="preserve">• Tự động chuẩn hóa chữ thường thành chữ hoa B01
-• Xác thực thành công vào Dashboard
-• Lưu Token ca trực hợp lệ</v>
-      </c>
-      <c r="M2" t="str">
-        <v>Không phân biệt chữ hoa, chữ thường</v>
-      </c>
-    </row>
-    <row r="3" xml:space="preserve">
-      <c r="A3" t="str">
-        <v>TC-AUTH-002</v>
-      </c>
-      <c r="B3" t="str">
-        <v>M01</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Đăng nhập với mã trạm không tồn tại trong CSDL</v>
-      </c>
-      <c r="D3" t="str">
-        <v>P2</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Ngoại lệ</v>
-      </c>
-      <c r="F3" t="str">
-        <v>REGRESSION</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Web Trực ban</v>
-      </c>
-      <c r="H3" t="str">
-        <v>SRS-AUTH-02</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Trực ban mở giao diện đăng nhập.</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Station Code = B999</v>
-      </c>
-      <c r="K3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Nhập mã trạm: B999
-2. Bấm Đăng nhập</v>
-      </c>
-      <c r="L3" t="str" xml:space="preserve">
-        <v xml:space="preserve">• Hiển thị thông báo lỗi: Mã trạm không tồn tại
-• Chặn truy cập vào hệ thống</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Kiểm tra thông báo thân thiện với người dùng</v>
-      </c>
-    </row>
-    <row r="4" xml:space="preserve">
-      <c r="A4" t="str">
-        <v>TC-CKIN-001</v>
-      </c>
-      <c r="B4" t="str">
-        <v>M02</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Tiếp đón khách đơn có quét thẻ CCCD gắn chip</v>
-      </c>
-      <c r="D4" t="str">
-        <v>P1</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Chức năng</v>
-      </c>
-      <c r="F4" t="str">
-        <v>REGRESSION</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Web Trực ban</v>
-      </c>
-      <c r="H4" t="str">
-        <v>SRS-CKIN-01</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Thiết bị đọc thẻ CCCD W3/EA09N kết nối online.</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Thẻ CCCD thử nghiệm hợp lệ</v>
-      </c>
-      <c r="K4" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Đặt thẻ CCCD lên máy đọc
-2. Bấm Đọc thẻ CCCD
-3. Nhập Mục đích: Liên hệ công việc.
-4. Bấm Check-in</v>
-      </c>
-      <c r="L4" t="str" xml:space="preserve">
-        <v xml:space="preserve">• Điền tự động Họ tên, CCCD, Ảnh chân dung
-• Mục đích mặc định là Liên hệ công việc.
-• Tạo lượt viếng thăm thành công</v>
-      </c>
-      <c r="M4" t="str">
-        <v>Mục đích vào làm việc mặc định là Liên hệ công việc.</v>
+    <row r="1" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+    </row>
+    <row r="3" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="30" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="17">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" s="26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" s="16" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
-  </ignoredErrors>
+  <autoFilter ref="A4:N4"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF6366F1"/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="65" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>